--- a/Azure_Remediation_ReportT.xlsx
+++ b/Azure_Remediation_ReportT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D354FD4-303B-441C-89AA-4550EC937332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889A2536-6AD9-4A57-B226-448B038D7AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{710A899D-571A-4743-BB8E-066A6642D9AD}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
-    <t>Command Tier</t>
-  </si>
-  <si>
     <t>Total Active Units</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Agency</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -887,7 +887,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4427509F-B8B3-4BC5-9BF7-75C056438784}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E13" xr:uid="{4427509F-B8B3-4BC5-9BF7-75C056438784}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{625F11CD-EEBE-4869-8353-A0895B828298}" name="Command Tier" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{625F11CD-EEBE-4869-8353-A0895B828298}" name="Region" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{D9A15808-24F5-4846-AB2B-CFD8E13595E5}" name="Agency" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{967908B7-A211-49A5-B467-1F05C9AC73BD}" name="Total Active Units" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{6C1A4BD7-53F7-4A3B-9F57-376788401CDF}" name="Precise Unit Cost (MSRP)" dataDxfId="1"/>
@@ -1226,27 +1226,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>36448246</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>32971705</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>32751775</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>32063260</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>32443716</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>31822170</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C8" s="1">
         <v>32880396</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>31853081</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>31460870</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
         <v>32202276</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>31532498</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="7">
         <v>29925570</v>
